--- a/NUMEX_pre_RStudio/models_leaf.xlsx
+++ b/NUMEX_pre_RStudio/models_leaf.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="400">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -747,6 +747,471 @@
   </si>
   <si>
     <t xml:space="preserve">-11.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1449.940***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(141.029)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(186.060)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-95.321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(195.115)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-24.395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(185.586)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">494.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">789.228***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(86.627)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(146.961)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-84.864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(93.524)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-31.610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(97.504)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">599.165***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(48.566)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-86.488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(72.034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-99.430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(76.789)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(65.158)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">558.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA| 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.961***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(26.066)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-12.251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(40.352)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-30.653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(37.594)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-60.866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(38.325)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">365.339***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(40.901)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-65.059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(51.495)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-48.814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(62.030)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(49.581)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.483***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.336)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.571)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.065)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.379)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.804***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12.226)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16.594)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(17.616)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16.786)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">462.214***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13.373)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(26.746)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-41.722+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(17.690)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.415***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.358)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.978)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11.667)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.909)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">485.305***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.590)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.419)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.671)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.884)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">276.601***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(15.797)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13.128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(19.052)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-28.263+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(15.276)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">458.366***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(18.138)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(25.651)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(33.934)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(24.559)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.1</t>
   </si>
 </sst>
 </file>
@@ -794,8 +1259,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O21" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:O21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O33" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:O33"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Modelo"/>
     <tableColumn id="2" name="estimates"/>
@@ -2086,6 +2551,570 @@
         <v>244</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>245</v>
+      </c>
+      <c r="B22" t="s">
+        <v>246</v>
+      </c>
+      <c r="C22" t="s">
+        <v>247</v>
+      </c>
+      <c r="D22" t="s">
+        <v>248</v>
+      </c>
+      <c r="E22" t="s">
+        <v>249</v>
+      </c>
+      <c r="F22" t="s">
+        <v>250</v>
+      </c>
+      <c r="G22" t="s">
+        <v>251</v>
+      </c>
+      <c r="H22" t="s">
+        <v>252</v>
+      </c>
+      <c r="I22" t="s">
+        <v>253</v>
+      </c>
+      <c r="J22" t="s">
+        <v>254</v>
+      </c>
+      <c r="K22" t="s">
+        <v>255</v>
+      </c>
+      <c r="L22" t="s">
+        <v>41</v>
+      </c>
+      <c r="M22" t="s">
+        <v>256</v>
+      </c>
+      <c r="N22" t="s">
+        <v>257</v>
+      </c>
+      <c r="O22" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>259</v>
+      </c>
+      <c r="B23" t="s">
+        <v>260</v>
+      </c>
+      <c r="C23" t="s">
+        <v>261</v>
+      </c>
+      <c r="D23" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" t="s">
+        <v>263</v>
+      </c>
+      <c r="F23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G23" t="s">
+        <v>265</v>
+      </c>
+      <c r="H23" t="s">
+        <v>266</v>
+      </c>
+      <c r="I23" t="s">
+        <v>267</v>
+      </c>
+      <c r="J23" t="s">
+        <v>268</v>
+      </c>
+      <c r="K23" t="s">
+        <v>269</v>
+      </c>
+      <c r="L23" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" t="s">
+        <v>270</v>
+      </c>
+      <c r="N23" t="s">
+        <v>271</v>
+      </c>
+      <c r="O23" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>273</v>
+      </c>
+      <c r="B24" t="s">
+        <v>274</v>
+      </c>
+      <c r="C24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D24" t="s">
+        <v>276</v>
+      </c>
+      <c r="E24" t="s">
+        <v>277</v>
+      </c>
+      <c r="F24" t="s">
+        <v>278</v>
+      </c>
+      <c r="G24" t="s">
+        <v>279</v>
+      </c>
+      <c r="H24" t="s">
+        <v>280</v>
+      </c>
+      <c r="I24" t="s">
+        <v>281</v>
+      </c>
+      <c r="J24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K24" t="s">
+        <v>282</v>
+      </c>
+      <c r="L24" t="s">
+        <v>70</v>
+      </c>
+      <c r="M24" t="s">
+        <v>283</v>
+      </c>
+      <c r="N24" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>285</v>
+      </c>
+      <c r="B25" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" t="s">
+        <v>287</v>
+      </c>
+      <c r="D25" t="s">
+        <v>288</v>
+      </c>
+      <c r="E25" t="s">
+        <v>289</v>
+      </c>
+      <c r="F25" t="s">
+        <v>290</v>
+      </c>
+      <c r="G25" t="s">
+        <v>291</v>
+      </c>
+      <c r="H25" t="s">
+        <v>292</v>
+      </c>
+      <c r="I25" t="s">
+        <v>293</v>
+      </c>
+      <c r="J25" t="s">
+        <v>294</v>
+      </c>
+      <c r="K25" t="s">
+        <v>295</v>
+      </c>
+      <c r="L25" t="s">
+        <v>84</v>
+      </c>
+      <c r="M25" t="s">
+        <v>296</v>
+      </c>
+      <c r="N25" t="s">
+        <v>297</v>
+      </c>
+      <c r="O25" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>299</v>
+      </c>
+      <c r="B26" t="s">
+        <v>300</v>
+      </c>
+      <c r="C26" t="s">
+        <v>301</v>
+      </c>
+      <c r="D26" t="s">
+        <v>302</v>
+      </c>
+      <c r="E26" t="s">
+        <v>303</v>
+      </c>
+      <c r="F26" t="s">
+        <v>304</v>
+      </c>
+      <c r="G26" t="s">
+        <v>305</v>
+      </c>
+      <c r="H26" t="s">
+        <v>306</v>
+      </c>
+      <c r="I26" t="s">
+        <v>307</v>
+      </c>
+      <c r="J26" t="s">
+        <v>308</v>
+      </c>
+      <c r="K26" t="s">
+        <v>309</v>
+      </c>
+      <c r="L26" t="s">
+        <v>96</v>
+      </c>
+      <c r="M26" t="s">
+        <v>310</v>
+      </c>
+      <c r="N26" t="s">
+        <v>311</v>
+      </c>
+      <c r="O26" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>313</v>
+      </c>
+      <c r="B27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C27" t="s">
+        <v>315</v>
+      </c>
+      <c r="D27" t="s">
+        <v>316</v>
+      </c>
+      <c r="E27" t="s">
+        <v>317</v>
+      </c>
+      <c r="F27" t="s">
+        <v>318</v>
+      </c>
+      <c r="G27" t="s">
+        <v>319</v>
+      </c>
+      <c r="H27" t="s">
+        <v>320</v>
+      </c>
+      <c r="I27" t="s">
+        <v>321</v>
+      </c>
+      <c r="J27" t="s">
+        <v>322</v>
+      </c>
+      <c r="K27" t="s">
+        <v>323</v>
+      </c>
+      <c r="L27" t="s">
+        <v>109</v>
+      </c>
+      <c r="M27" t="s">
+        <v>283</v>
+      </c>
+      <c r="N27" t="s">
+        <v>324</v>
+      </c>
+      <c r="O27" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B28" t="s">
+        <v>327</v>
+      </c>
+      <c r="C28" t="s">
+        <v>328</v>
+      </c>
+      <c r="D28" t="s">
+        <v>329</v>
+      </c>
+      <c r="E28" t="s">
+        <v>330</v>
+      </c>
+      <c r="F28" t="s">
+        <v>331</v>
+      </c>
+      <c r="G28" t="s">
+        <v>332</v>
+      </c>
+      <c r="H28" t="s">
+        <v>333</v>
+      </c>
+      <c r="I28" t="s">
+        <v>334</v>
+      </c>
+      <c r="J28" t="s">
+        <v>335</v>
+      </c>
+      <c r="K28" t="s">
+        <v>336</v>
+      </c>
+      <c r="L28" t="s">
+        <v>41</v>
+      </c>
+      <c r="M28" t="s">
+        <v>337</v>
+      </c>
+      <c r="N28" t="s">
+        <v>338</v>
+      </c>
+      <c r="O28" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>340</v>
+      </c>
+      <c r="B29" t="s">
+        <v>341</v>
+      </c>
+      <c r="C29" t="s">
+        <v>342</v>
+      </c>
+      <c r="D29" t="s">
+        <v>343</v>
+      </c>
+      <c r="E29" t="s">
+        <v>344</v>
+      </c>
+      <c r="F29" t="s">
+        <v>345</v>
+      </c>
+      <c r="G29" t="s">
+        <v>346</v>
+      </c>
+      <c r="H29" t="s">
+        <v>347</v>
+      </c>
+      <c r="I29" t="s">
+        <v>346</v>
+      </c>
+      <c r="J29" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" t="s">
+        <v>348</v>
+      </c>
+      <c r="L29" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" t="s">
+        <v>349</v>
+      </c>
+      <c r="N29" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>351</v>
+      </c>
+      <c r="B30" t="s">
+        <v>352</v>
+      </c>
+      <c r="C30" t="s">
+        <v>353</v>
+      </c>
+      <c r="D30" t="s">
+        <v>354</v>
+      </c>
+      <c r="E30" t="s">
+        <v>355</v>
+      </c>
+      <c r="F30" t="s">
+        <v>356</v>
+      </c>
+      <c r="G30" t="s">
+        <v>357</v>
+      </c>
+      <c r="H30" t="s">
+        <v>358</v>
+      </c>
+      <c r="I30" t="s">
+        <v>359</v>
+      </c>
+      <c r="J30" t="s">
+        <v>360</v>
+      </c>
+      <c r="K30" t="s">
+        <v>361</v>
+      </c>
+      <c r="L30" t="s">
+        <v>70</v>
+      </c>
+      <c r="M30" t="s">
+        <v>362</v>
+      </c>
+      <c r="N30" t="s">
+        <v>363</v>
+      </c>
+      <c r="O30" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>365</v>
+      </c>
+      <c r="B31" t="s">
+        <v>366</v>
+      </c>
+      <c r="C31" t="s">
+        <v>367</v>
+      </c>
+      <c r="D31" t="s">
+        <v>368</v>
+      </c>
+      <c r="E31" t="s">
+        <v>369</v>
+      </c>
+      <c r="F31" t="s">
+        <v>370</v>
+      </c>
+      <c r="G31" t="s">
+        <v>371</v>
+      </c>
+      <c r="H31" t="s">
+        <v>372</v>
+      </c>
+      <c r="I31" t="s">
+        <v>373</v>
+      </c>
+      <c r="J31" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" t="s">
+        <v>374</v>
+      </c>
+      <c r="L31" t="s">
+        <v>84</v>
+      </c>
+      <c r="M31" t="s">
+        <v>375</v>
+      </c>
+      <c r="N31" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>377</v>
+      </c>
+      <c r="B32" t="s">
+        <v>378</v>
+      </c>
+      <c r="C32" t="s">
+        <v>357</v>
+      </c>
+      <c r="D32" t="s">
+        <v>379</v>
+      </c>
+      <c r="E32" t="s">
+        <v>380</v>
+      </c>
+      <c r="F32" t="s">
+        <v>381</v>
+      </c>
+      <c r="G32" t="s">
+        <v>382</v>
+      </c>
+      <c r="H32" t="s">
+        <v>383</v>
+      </c>
+      <c r="I32" t="s">
+        <v>384</v>
+      </c>
+      <c r="J32" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" t="s">
+        <v>385</v>
+      </c>
+      <c r="L32" t="s">
+        <v>96</v>
+      </c>
+      <c r="M32" t="s">
+        <v>386</v>
+      </c>
+      <c r="N32" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>388</v>
+      </c>
+      <c r="B33" t="s">
+        <v>389</v>
+      </c>
+      <c r="C33" t="s">
+        <v>390</v>
+      </c>
+      <c r="D33" t="s">
+        <v>391</v>
+      </c>
+      <c r="E33" t="s">
+        <v>392</v>
+      </c>
+      <c r="F33" t="s">
+        <v>393</v>
+      </c>
+      <c r="G33" t="s">
+        <v>394</v>
+      </c>
+      <c r="H33" t="s">
+        <v>395</v>
+      </c>
+      <c r="I33" t="s">
+        <v>396</v>
+      </c>
+      <c r="J33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" t="s">
+        <v>397</v>
+      </c>
+      <c r="L33" t="s">
+        <v>109</v>
+      </c>
+      <c r="M33" t="s">
+        <v>398</v>
+      </c>
+      <c r="N33" t="s">
+        <v>29</v>
+      </c>
+      <c r="O33" t="s">
+        <v>399</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/NUMEX_pre_RStudio/models_leaf.xlsx
+++ b/NUMEX_pre_RStudio/models_leaf.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">(Intercept)</t>
   </si>
   <si>
-    <t xml:space="preserve">SUBN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBNP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUBP</t>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N × P</t>
   </si>
   <si>
     <t xml:space="preserve">SD (Intercept Bloque)</t>
@@ -119,18 +119,18 @@
     <t xml:space="preserve">(4.829)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.344)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-2.247</t>
   </si>
   <si>
     <t xml:space="preserve">(5.136)</t>
   </si>
   <si>
+    <t xml:space="preserve">3.538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.486)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.000</t>
   </si>
   <si>
@@ -161,18 +161,18 @@
     <t xml:space="preserve">(7.724)</t>
   </si>
   <si>
-    <t xml:space="preserve">14.369*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.867)</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.687</t>
   </si>
   <si>
     <t xml:space="preserve">(5.135)</t>
   </si>
   <si>
+    <t xml:space="preserve">-17.815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.798)</t>
+  </si>
+  <si>
     <t xml:space="preserve">7.217</t>
   </si>
   <si>
@@ -206,18 +206,18 @@
     <t xml:space="preserve">(1.762)</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.875)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.383</t>
   </si>
   <si>
     <t xml:space="preserve">(1.592)</t>
   </si>
   <si>
+    <t xml:space="preserve">-3.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.523)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.357</t>
   </si>
   <si>
@@ -251,18 +251,18 @@
     <t xml:space="preserve">(1.359)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.261)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-1.871</t>
   </si>
   <si>
     <t xml:space="preserve">(1.289)</t>
   </si>
   <si>
+    <t xml:space="preserve">2.327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.903)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.329</t>
   </si>
   <si>
@@ -287,18 +287,18 @@
     <t xml:space="preserve">(6.954)</t>
   </si>
   <si>
-    <t xml:space="preserve">-2.907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8.387)</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.024</t>
   </si>
   <si>
     <t xml:space="preserve">(6.725)</t>
   </si>
   <si>
+    <t xml:space="preserve">-1.918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.544)</t>
+  </si>
+  <si>
     <t xml:space="preserve">11.484</t>
   </si>
   <si>
@@ -326,18 +326,18 @@
     <t xml:space="preserve">(4.255)</t>
   </si>
   <si>
-    <t xml:space="preserve">2.106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5.629)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.477</t>
   </si>
   <si>
     <t xml:space="preserve">(4.074)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.948)</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.728</t>
   </si>
   <si>
@@ -365,13 +365,16 @@
     <t xml:space="preserve">(0.010)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.011</t>
+    <t xml:space="preserve">-0.001</t>
   </si>
   <si>
     <t xml:space="preserve">(0.011)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.001</t>
+    <t xml:space="preserve">-0.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.016)</t>
   </si>
   <si>
     <t xml:space="preserve">0.024</t>
@@ -398,13 +401,16 @@
     <t xml:space="preserve">(0.006)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.008+</t>
+    <t xml:space="preserve">0.002</t>
   </si>
   <si>
     <t xml:space="preserve">(0.004)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.002</t>
+    <t xml:space="preserve">0.027*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.008)</t>
   </si>
   <si>
     <t xml:space="preserve">0.023</t>
@@ -428,171 +434,180 @@
     <t xml:space="preserve">0.543***</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.016)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.023</t>
   </si>
   <si>
     <t xml:space="preserve">(0.022)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.031)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-105.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thickness | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.478***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.015)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-182.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thickness | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.460***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.017)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-44.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thickness | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.266***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.034)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-37.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.782***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.040)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.059)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.062)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.091)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.955***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.083)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.153)</t>
+  </si>
+  <si>
     <t xml:space="preserve">-0.007</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.023)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.020)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-105.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thickness | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.478***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-182.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thickness | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.460***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.017)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.028)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-44.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thickness | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.266***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.015)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.021)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-37.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.782***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.040)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.059)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.065)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.062)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-17.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.955***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.083)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.153)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.098)</t>
-  </si>
-  <si>
     <t xml:space="preserve">(0.101)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.188)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.067</t>
   </si>
   <si>
@@ -623,18 +638,18 @@
     <t xml:space="preserve">(0.060)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.112+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.064)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.117*</t>
   </si>
   <si>
     <t xml:space="preserve">(0.054)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.086)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.047</t>
   </si>
   <si>
@@ -662,13 +677,13 @@
     <t xml:space="preserve">-0.025</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.034)</t>
+    <t xml:space="preserve">-0.024</t>
   </si>
   <si>
     <t xml:space="preserve">(0.033)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.024</t>
+    <t xml:space="preserve">(0.049)</t>
   </si>
   <si>
     <t xml:space="preserve">0.076</t>
@@ -695,15 +710,18 @@
     <t xml:space="preserve">(0.092)</t>
   </si>
   <si>
-    <t xml:space="preserve">(0.111)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-0.159+</t>
   </si>
   <si>
     <t xml:space="preserve">(0.089)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.139)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.055</t>
   </si>
   <si>
@@ -731,487 +749,22 @@
     <t xml:space="preserve">(0.053)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.071)</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.050</t>
   </si>
   <si>
     <t xml:space="preserve">(0.051)</t>
   </si>
   <si>
+    <t xml:space="preserve">0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.087)</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.093</t>
   </si>
   <si>
     <t xml:space="preserve">-11.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1449.940***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(141.029)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-10.168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(186.060)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-95.321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(195.115)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-24.395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(185.586)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">494.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">789.228***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(86.627)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(146.961)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-84.864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(93.524)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-31.610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(97.504)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">599.165***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(48.566)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-86.488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(72.034)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-99.430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(76.789)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(65.158)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">558.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA| 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.961***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(26.066)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-12.251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(40.352)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-30.653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(37.594)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-60.866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(38.325)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">575.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">365.339***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(40.901)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-65.059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(51.495)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-48.814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(62.030)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(49.581)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.290</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.483***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3.336)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.780</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.571)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.065)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4.379)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.804***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(12.226)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(16.594)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(17.616)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-17.703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(16.786)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMC | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">462.214***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(13.373)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-17.635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(26.746)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-41.722+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(17.690)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMC | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">431.415***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.358)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.978)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(11.667)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.909)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMC 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">485.305***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6.590)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(10.419)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.671)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9.884)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMC | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">276.601***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(15.797)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-13.128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(19.052)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-28.263+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(15.276)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMC | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">458.366***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(18.138)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(25.651)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(33.934)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(24.559)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.1</t>
   </si>
 </sst>
 </file>
@@ -1259,8 +812,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O33" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:O33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O21" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:O21"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Modelo"/>
     <tableColumn id="2" name="estimates"/>
@@ -1901,7 +1454,7 @@
         <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
         <v>89</v>
@@ -2013,98 +1566,98 @@
         <v>119</v>
       </c>
       <c r="I10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J10" t="s">
         <v>39</v>
       </c>
       <c r="K10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L10" t="s">
         <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N10" t="s">
         <v>29</v>
       </c>
       <c r="O10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I11" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s">
         <v>55</v>
       </c>
       <c r="M11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H12" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="I12" t="s">
         <v>144</v>
@@ -2154,54 +1707,54 @@
         <v>154</v>
       </c>
       <c r="I13" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="J13" t="s">
         <v>39</v>
       </c>
       <c r="K13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s">
         <v>84</v>
       </c>
       <c r="M13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s">
         <v>29</v>
       </c>
       <c r="O13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E14" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="F14" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="G14" t="s">
         <v>163</v>
       </c>
       <c r="H14" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="I14" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="J14" t="s">
         <v>39</v>
@@ -2213,236 +1766,236 @@
         <v>96</v>
       </c>
       <c r="M14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s">
         <v>29</v>
       </c>
       <c r="O14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F15" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G15" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="H15" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="I15" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="J15" t="s">
         <v>39</v>
       </c>
       <c r="K15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s">
         <v>109</v>
       </c>
       <c r="M15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s">
         <v>29</v>
       </c>
       <c r="O15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F16" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G16" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H16" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I16" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J16" t="s">
         <v>39</v>
       </c>
       <c r="K16" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s">
         <v>41</v>
       </c>
       <c r="M16" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s">
         <v>29</v>
       </c>
       <c r="O16" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E17" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F17" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="G17" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H17" t="s">
-        <v>141</v>
+        <v>196</v>
       </c>
       <c r="I17" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J17" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K17" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="L17" t="s">
         <v>55</v>
       </c>
       <c r="M17" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="N17" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="O17" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C18" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D18" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E18" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F18" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G18" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H18" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="I18" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="J18" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K18" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L18" t="s">
         <v>70</v>
       </c>
       <c r="M18" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="O18" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C19" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E19" t="s">
-        <v>216</v>
+        <v>173</v>
       </c>
       <c r="F19" t="s">
-        <v>119</v>
+        <v>221</v>
       </c>
       <c r="G19" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H19" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="I19" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="J19" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="L19" t="s">
         <v>84</v>
@@ -2451,668 +2004,104 @@
         <v>145</v>
       </c>
       <c r="N19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="O19" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="D20" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F20" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="G20" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="H20" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="I20" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="J20" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="K20" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="L20" t="s">
         <v>96</v>
       </c>
       <c r="M20" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="N20" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="O20" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B21" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C21" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E21" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="F21" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G21" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="H21" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="I21" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="J21" t="s">
         <v>39</v>
       </c>
       <c r="K21" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="L21" t="s">
         <v>109</v>
       </c>
       <c r="M21" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="N21" t="s">
         <v>29</v>
       </c>
       <c r="O21" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>245</v>
-      </c>
-      <c r="B22" t="s">
-        <v>246</v>
-      </c>
-      <c r="C22" t="s">
-        <v>247</v>
-      </c>
-      <c r="D22" t="s">
-        <v>248</v>
-      </c>
-      <c r="E22" t="s">
-        <v>249</v>
-      </c>
-      <c r="F22" t="s">
         <v>250</v>
-      </c>
-      <c r="G22" t="s">
-        <v>251</v>
-      </c>
-      <c r="H22" t="s">
-        <v>252</v>
-      </c>
-      <c r="I22" t="s">
-        <v>253</v>
-      </c>
-      <c r="J22" t="s">
-        <v>254</v>
-      </c>
-      <c r="K22" t="s">
-        <v>255</v>
-      </c>
-      <c r="L22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M22" t="s">
-        <v>256</v>
-      </c>
-      <c r="N22" t="s">
-        <v>257</v>
-      </c>
-      <c r="O22" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>259</v>
-      </c>
-      <c r="B23" t="s">
-        <v>260</v>
-      </c>
-      <c r="C23" t="s">
-        <v>261</v>
-      </c>
-      <c r="D23" t="s">
-        <v>262</v>
-      </c>
-      <c r="E23" t="s">
-        <v>263</v>
-      </c>
-      <c r="F23" t="s">
-        <v>264</v>
-      </c>
-      <c r="G23" t="s">
-        <v>265</v>
-      </c>
-      <c r="H23" t="s">
-        <v>266</v>
-      </c>
-      <c r="I23" t="s">
-        <v>267</v>
-      </c>
-      <c r="J23" t="s">
-        <v>268</v>
-      </c>
-      <c r="K23" t="s">
-        <v>269</v>
-      </c>
-      <c r="L23" t="s">
-        <v>55</v>
-      </c>
-      <c r="M23" t="s">
-        <v>270</v>
-      </c>
-      <c r="N23" t="s">
-        <v>271</v>
-      </c>
-      <c r="O23" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>273</v>
-      </c>
-      <c r="B24" t="s">
-        <v>274</v>
-      </c>
-      <c r="C24" t="s">
-        <v>275</v>
-      </c>
-      <c r="D24" t="s">
-        <v>276</v>
-      </c>
-      <c r="E24" t="s">
-        <v>277</v>
-      </c>
-      <c r="F24" t="s">
-        <v>278</v>
-      </c>
-      <c r="G24" t="s">
-        <v>279</v>
-      </c>
-      <c r="H24" t="s">
-        <v>280</v>
-      </c>
-      <c r="I24" t="s">
-        <v>281</v>
-      </c>
-      <c r="J24" t="s">
-        <v>39</v>
-      </c>
-      <c r="K24" t="s">
-        <v>282</v>
-      </c>
-      <c r="L24" t="s">
-        <v>70</v>
-      </c>
-      <c r="M24" t="s">
-        <v>283</v>
-      </c>
-      <c r="N24" t="s">
-        <v>29</v>
-      </c>
-      <c r="O24" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>285</v>
-      </c>
-      <c r="B25" t="s">
-        <v>286</v>
-      </c>
-      <c r="C25" t="s">
-        <v>287</v>
-      </c>
-      <c r="D25" t="s">
-        <v>288</v>
-      </c>
-      <c r="E25" t="s">
-        <v>289</v>
-      </c>
-      <c r="F25" t="s">
-        <v>290</v>
-      </c>
-      <c r="G25" t="s">
-        <v>291</v>
-      </c>
-      <c r="H25" t="s">
-        <v>292</v>
-      </c>
-      <c r="I25" t="s">
-        <v>293</v>
-      </c>
-      <c r="J25" t="s">
-        <v>294</v>
-      </c>
-      <c r="K25" t="s">
-        <v>295</v>
-      </c>
-      <c r="L25" t="s">
-        <v>84</v>
-      </c>
-      <c r="M25" t="s">
-        <v>296</v>
-      </c>
-      <c r="N25" t="s">
-        <v>297</v>
-      </c>
-      <c r="O25" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>299</v>
-      </c>
-      <c r="B26" t="s">
-        <v>300</v>
-      </c>
-      <c r="C26" t="s">
-        <v>301</v>
-      </c>
-      <c r="D26" t="s">
-        <v>302</v>
-      </c>
-      <c r="E26" t="s">
-        <v>303</v>
-      </c>
-      <c r="F26" t="s">
-        <v>304</v>
-      </c>
-      <c r="G26" t="s">
-        <v>305</v>
-      </c>
-      <c r="H26" t="s">
-        <v>306</v>
-      </c>
-      <c r="I26" t="s">
-        <v>307</v>
-      </c>
-      <c r="J26" t="s">
-        <v>308</v>
-      </c>
-      <c r="K26" t="s">
-        <v>309</v>
-      </c>
-      <c r="L26" t="s">
-        <v>96</v>
-      </c>
-      <c r="M26" t="s">
-        <v>310</v>
-      </c>
-      <c r="N26" t="s">
-        <v>311</v>
-      </c>
-      <c r="O26" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>313</v>
-      </c>
-      <c r="B27" t="s">
-        <v>314</v>
-      </c>
-      <c r="C27" t="s">
-        <v>315</v>
-      </c>
-      <c r="D27" t="s">
-        <v>316</v>
-      </c>
-      <c r="E27" t="s">
-        <v>317</v>
-      </c>
-      <c r="F27" t="s">
-        <v>318</v>
-      </c>
-      <c r="G27" t="s">
-        <v>319</v>
-      </c>
-      <c r="H27" t="s">
-        <v>320</v>
-      </c>
-      <c r="I27" t="s">
-        <v>321</v>
-      </c>
-      <c r="J27" t="s">
-        <v>322</v>
-      </c>
-      <c r="K27" t="s">
-        <v>323</v>
-      </c>
-      <c r="L27" t="s">
-        <v>109</v>
-      </c>
-      <c r="M27" t="s">
-        <v>283</v>
-      </c>
-      <c r="N27" t="s">
-        <v>324</v>
-      </c>
-      <c r="O27" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>326</v>
-      </c>
-      <c r="B28" t="s">
-        <v>327</v>
-      </c>
-      <c r="C28" t="s">
-        <v>328</v>
-      </c>
-      <c r="D28" t="s">
-        <v>329</v>
-      </c>
-      <c r="E28" t="s">
-        <v>330</v>
-      </c>
-      <c r="F28" t="s">
-        <v>331</v>
-      </c>
-      <c r="G28" t="s">
-        <v>332</v>
-      </c>
-      <c r="H28" t="s">
-        <v>333</v>
-      </c>
-      <c r="I28" t="s">
-        <v>334</v>
-      </c>
-      <c r="J28" t="s">
-        <v>335</v>
-      </c>
-      <c r="K28" t="s">
-        <v>336</v>
-      </c>
-      <c r="L28" t="s">
-        <v>41</v>
-      </c>
-      <c r="M28" t="s">
-        <v>337</v>
-      </c>
-      <c r="N28" t="s">
-        <v>338</v>
-      </c>
-      <c r="O28" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>340</v>
-      </c>
-      <c r="B29" t="s">
-        <v>341</v>
-      </c>
-      <c r="C29" t="s">
-        <v>342</v>
-      </c>
-      <c r="D29" t="s">
-        <v>343</v>
-      </c>
-      <c r="E29" t="s">
-        <v>344</v>
-      </c>
-      <c r="F29" t="s">
-        <v>345</v>
-      </c>
-      <c r="G29" t="s">
-        <v>346</v>
-      </c>
-      <c r="H29" t="s">
-        <v>347</v>
-      </c>
-      <c r="I29" t="s">
-        <v>346</v>
-      </c>
-      <c r="J29" t="s">
-        <v>39</v>
-      </c>
-      <c r="K29" t="s">
-        <v>348</v>
-      </c>
-      <c r="L29" t="s">
-        <v>55</v>
-      </c>
-      <c r="M29" t="s">
-        <v>349</v>
-      </c>
-      <c r="N29" t="s">
-        <v>29</v>
-      </c>
-      <c r="O29" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>351</v>
-      </c>
-      <c r="B30" t="s">
-        <v>352</v>
-      </c>
-      <c r="C30" t="s">
-        <v>353</v>
-      </c>
-      <c r="D30" t="s">
-        <v>354</v>
-      </c>
-      <c r="E30" t="s">
-        <v>355</v>
-      </c>
-      <c r="F30" t="s">
-        <v>356</v>
-      </c>
-      <c r="G30" t="s">
-        <v>357</v>
-      </c>
-      <c r="H30" t="s">
-        <v>358</v>
-      </c>
-      <c r="I30" t="s">
-        <v>359</v>
-      </c>
-      <c r="J30" t="s">
-        <v>360</v>
-      </c>
-      <c r="K30" t="s">
-        <v>361</v>
-      </c>
-      <c r="L30" t="s">
-        <v>70</v>
-      </c>
-      <c r="M30" t="s">
-        <v>362</v>
-      </c>
-      <c r="N30" t="s">
-        <v>363</v>
-      </c>
-      <c r="O30" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>365</v>
-      </c>
-      <c r="B31" t="s">
-        <v>366</v>
-      </c>
-      <c r="C31" t="s">
-        <v>367</v>
-      </c>
-      <c r="D31" t="s">
-        <v>368</v>
-      </c>
-      <c r="E31" t="s">
-        <v>369</v>
-      </c>
-      <c r="F31" t="s">
-        <v>370</v>
-      </c>
-      <c r="G31" t="s">
-        <v>371</v>
-      </c>
-      <c r="H31" t="s">
-        <v>372</v>
-      </c>
-      <c r="I31" t="s">
-        <v>373</v>
-      </c>
-      <c r="J31" t="s">
-        <v>39</v>
-      </c>
-      <c r="K31" t="s">
-        <v>374</v>
-      </c>
-      <c r="L31" t="s">
-        <v>84</v>
-      </c>
-      <c r="M31" t="s">
-        <v>375</v>
-      </c>
-      <c r="N31" t="s">
-        <v>29</v>
-      </c>
-      <c r="O31" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>377</v>
-      </c>
-      <c r="B32" t="s">
-        <v>378</v>
-      </c>
-      <c r="C32" t="s">
-        <v>357</v>
-      </c>
-      <c r="D32" t="s">
-        <v>379</v>
-      </c>
-      <c r="E32" t="s">
-        <v>380</v>
-      </c>
-      <c r="F32" t="s">
-        <v>381</v>
-      </c>
-      <c r="G32" t="s">
-        <v>382</v>
-      </c>
-      <c r="H32" t="s">
-        <v>383</v>
-      </c>
-      <c r="I32" t="s">
-        <v>384</v>
-      </c>
-      <c r="J32" t="s">
-        <v>39</v>
-      </c>
-      <c r="K32" t="s">
-        <v>385</v>
-      </c>
-      <c r="L32" t="s">
-        <v>96</v>
-      </c>
-      <c r="M32" t="s">
-        <v>386</v>
-      </c>
-      <c r="N32" t="s">
-        <v>29</v>
-      </c>
-      <c r="O32" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>388</v>
-      </c>
-      <c r="B33" t="s">
-        <v>389</v>
-      </c>
-      <c r="C33" t="s">
-        <v>390</v>
-      </c>
-      <c r="D33" t="s">
-        <v>391</v>
-      </c>
-      <c r="E33" t="s">
-        <v>392</v>
-      </c>
-      <c r="F33" t="s">
-        <v>393</v>
-      </c>
-      <c r="G33" t="s">
-        <v>394</v>
-      </c>
-      <c r="H33" t="s">
-        <v>395</v>
-      </c>
-      <c r="I33" t="s">
-        <v>396</v>
-      </c>
-      <c r="J33" t="s">
-        <v>39</v>
-      </c>
-      <c r="K33" t="s">
-        <v>397</v>
-      </c>
-      <c r="L33" t="s">
-        <v>109</v>
-      </c>
-      <c r="M33" t="s">
-        <v>398</v>
-      </c>
-      <c r="N33" t="s">
-        <v>29</v>
-      </c>
-      <c r="O33" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/NUMEX_pre_RStudio/models_leaf.xlsx
+++ b/NUMEX_pre_RStudio/models_leaf.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="406">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -765,6 +765,471 @@
   </si>
   <si>
     <t xml:space="preserve">-11.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.913***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.060)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.175)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.095)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13.586)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.461***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.331)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7.348)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4.875)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.167)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.958***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.428)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.602)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.258)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5.151)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA| 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.998***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.303)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.916)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.830)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.520</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.267***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.045)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.575)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2.479)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(3.890)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.474***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.167)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.229)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.219)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.372)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.804***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(12.226)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16.594)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(16.786)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(24.885)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">462.214***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(13.373)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(26.746)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(17.690)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(31.362)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">431.415***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.358)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.978)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.909)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(15.718)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">485.305***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6.590)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(10.419)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9.884)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(14.593)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">276.601***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(11.667)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(15.797)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-28.263+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(15.276)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(23.951)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">458.366***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(18.138)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(25.651)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(24.559)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-29.509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(41.888)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.1</t>
   </si>
 </sst>
 </file>
@@ -812,8 +1277,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O21" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:O21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:O33" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:O33"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Modelo"/>
     <tableColumn id="2" name="estimates"/>
@@ -2104,6 +2569,570 @@
         <v>250</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>251</v>
+      </c>
+      <c r="B22" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" t="s">
+        <v>253</v>
+      </c>
+      <c r="D22" t="s">
+        <v>254</v>
+      </c>
+      <c r="E22" t="s">
+        <v>255</v>
+      </c>
+      <c r="F22" t="s">
+        <v>256</v>
+      </c>
+      <c r="G22" t="s">
+        <v>257</v>
+      </c>
+      <c r="H22" t="s">
+        <v>258</v>
+      </c>
+      <c r="I22" t="s">
+        <v>259</v>
+      </c>
+      <c r="J22" t="s">
+        <v>260</v>
+      </c>
+      <c r="K22" t="s">
+        <v>261</v>
+      </c>
+      <c r="L22" t="s">
+        <v>41</v>
+      </c>
+      <c r="M22" t="s">
+        <v>247</v>
+      </c>
+      <c r="N22" t="s">
+        <v>262</v>
+      </c>
+      <c r="O22" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>264</v>
+      </c>
+      <c r="B23" t="s">
+        <v>265</v>
+      </c>
+      <c r="C23" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" t="s">
+        <v>268</v>
+      </c>
+      <c r="F23" t="s">
+        <v>269</v>
+      </c>
+      <c r="G23" t="s">
+        <v>270</v>
+      </c>
+      <c r="H23" t="s">
+        <v>271</v>
+      </c>
+      <c r="I23" t="s">
+        <v>272</v>
+      </c>
+      <c r="J23" t="s">
+        <v>273</v>
+      </c>
+      <c r="K23" t="s">
+        <v>274</v>
+      </c>
+      <c r="L23" t="s">
+        <v>55</v>
+      </c>
+      <c r="M23" t="s">
+        <v>275</v>
+      </c>
+      <c r="N23" t="s">
+        <v>276</v>
+      </c>
+      <c r="O23" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>278</v>
+      </c>
+      <c r="B24" t="s">
+        <v>279</v>
+      </c>
+      <c r="C24" t="s">
+        <v>280</v>
+      </c>
+      <c r="D24" t="s">
+        <v>281</v>
+      </c>
+      <c r="E24" t="s">
+        <v>282</v>
+      </c>
+      <c r="F24" t="s">
+        <v>283</v>
+      </c>
+      <c r="G24" t="s">
+        <v>284</v>
+      </c>
+      <c r="H24" t="s">
+        <v>285</v>
+      </c>
+      <c r="I24" t="s">
+        <v>286</v>
+      </c>
+      <c r="J24" t="s">
+        <v>39</v>
+      </c>
+      <c r="K24" t="s">
+        <v>287</v>
+      </c>
+      <c r="L24" t="s">
+        <v>70</v>
+      </c>
+      <c r="M24" t="s">
+        <v>288</v>
+      </c>
+      <c r="N24" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>290</v>
+      </c>
+      <c r="B25" t="s">
+        <v>291</v>
+      </c>
+      <c r="C25" t="s">
+        <v>292</v>
+      </c>
+      <c r="D25" t="s">
+        <v>293</v>
+      </c>
+      <c r="E25" t="s">
+        <v>294</v>
+      </c>
+      <c r="F25" t="s">
+        <v>295</v>
+      </c>
+      <c r="G25" t="s">
+        <v>296</v>
+      </c>
+      <c r="H25" t="s">
+        <v>297</v>
+      </c>
+      <c r="I25" t="s">
+        <v>298</v>
+      </c>
+      <c r="J25" t="s">
+        <v>299</v>
+      </c>
+      <c r="K25" t="s">
+        <v>300</v>
+      </c>
+      <c r="L25" t="s">
+        <v>84</v>
+      </c>
+      <c r="M25" t="s">
+        <v>301</v>
+      </c>
+      <c r="N25" t="s">
+        <v>302</v>
+      </c>
+      <c r="O25" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>304</v>
+      </c>
+      <c r="B26" t="s">
+        <v>305</v>
+      </c>
+      <c r="C26" t="s">
+        <v>306</v>
+      </c>
+      <c r="D26" t="s">
+        <v>307</v>
+      </c>
+      <c r="E26" t="s">
+        <v>308</v>
+      </c>
+      <c r="F26" t="s">
+        <v>309</v>
+      </c>
+      <c r="G26" t="s">
+        <v>310</v>
+      </c>
+      <c r="H26" t="s">
+        <v>311</v>
+      </c>
+      <c r="I26" t="s">
+        <v>312</v>
+      </c>
+      <c r="J26" t="s">
+        <v>313</v>
+      </c>
+      <c r="K26" t="s">
+        <v>314</v>
+      </c>
+      <c r="L26" t="s">
+        <v>96</v>
+      </c>
+      <c r="M26" t="s">
+        <v>315</v>
+      </c>
+      <c r="N26" t="s">
+        <v>316</v>
+      </c>
+      <c r="O26" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>318</v>
+      </c>
+      <c r="B27" t="s">
+        <v>319</v>
+      </c>
+      <c r="C27" t="s">
+        <v>320</v>
+      </c>
+      <c r="D27" t="s">
+        <v>321</v>
+      </c>
+      <c r="E27" t="s">
+        <v>322</v>
+      </c>
+      <c r="F27" t="s">
+        <v>323</v>
+      </c>
+      <c r="G27" t="s">
+        <v>324</v>
+      </c>
+      <c r="H27" t="s">
+        <v>325</v>
+      </c>
+      <c r="I27" t="s">
+        <v>326</v>
+      </c>
+      <c r="J27" t="s">
+        <v>327</v>
+      </c>
+      <c r="K27" t="s">
+        <v>328</v>
+      </c>
+      <c r="L27" t="s">
+        <v>109</v>
+      </c>
+      <c r="M27" t="s">
+        <v>288</v>
+      </c>
+      <c r="N27" t="s">
+        <v>106</v>
+      </c>
+      <c r="O27" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>330</v>
+      </c>
+      <c r="B28" t="s">
+        <v>331</v>
+      </c>
+      <c r="C28" t="s">
+        <v>332</v>
+      </c>
+      <c r="D28" t="s">
+        <v>333</v>
+      </c>
+      <c r="E28" t="s">
+        <v>334</v>
+      </c>
+      <c r="F28" t="s">
+        <v>335</v>
+      </c>
+      <c r="G28" t="s">
+        <v>336</v>
+      </c>
+      <c r="H28" t="s">
+        <v>337</v>
+      </c>
+      <c r="I28" t="s">
+        <v>338</v>
+      </c>
+      <c r="J28" t="s">
+        <v>339</v>
+      </c>
+      <c r="K28" t="s">
+        <v>340</v>
+      </c>
+      <c r="L28" t="s">
+        <v>41</v>
+      </c>
+      <c r="M28" t="s">
+        <v>341</v>
+      </c>
+      <c r="N28" t="s">
+        <v>342</v>
+      </c>
+      <c r="O28" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>344</v>
+      </c>
+      <c r="B29" t="s">
+        <v>345</v>
+      </c>
+      <c r="C29" t="s">
+        <v>346</v>
+      </c>
+      <c r="D29" t="s">
+        <v>347</v>
+      </c>
+      <c r="E29" t="s">
+        <v>348</v>
+      </c>
+      <c r="F29" t="s">
+        <v>349</v>
+      </c>
+      <c r="G29" t="s">
+        <v>350</v>
+      </c>
+      <c r="H29" t="s">
+        <v>351</v>
+      </c>
+      <c r="I29" t="s">
+        <v>352</v>
+      </c>
+      <c r="J29" t="s">
+        <v>39</v>
+      </c>
+      <c r="K29" t="s">
+        <v>353</v>
+      </c>
+      <c r="L29" t="s">
+        <v>55</v>
+      </c>
+      <c r="M29" t="s">
+        <v>354</v>
+      </c>
+      <c r="N29" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B30" t="s">
+        <v>357</v>
+      </c>
+      <c r="C30" t="s">
+        <v>358</v>
+      </c>
+      <c r="D30" t="s">
+        <v>359</v>
+      </c>
+      <c r="E30" t="s">
+        <v>360</v>
+      </c>
+      <c r="F30" t="s">
+        <v>361</v>
+      </c>
+      <c r="G30" t="s">
+        <v>362</v>
+      </c>
+      <c r="H30" t="s">
+        <v>363</v>
+      </c>
+      <c r="I30" t="s">
+        <v>364</v>
+      </c>
+      <c r="J30" t="s">
+        <v>365</v>
+      </c>
+      <c r="K30" t="s">
+        <v>366</v>
+      </c>
+      <c r="L30" t="s">
+        <v>70</v>
+      </c>
+      <c r="M30" t="s">
+        <v>367</v>
+      </c>
+      <c r="N30" t="s">
+        <v>368</v>
+      </c>
+      <c r="O30" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>370</v>
+      </c>
+      <c r="B31" t="s">
+        <v>371</v>
+      </c>
+      <c r="C31" t="s">
+        <v>372</v>
+      </c>
+      <c r="D31" t="s">
+        <v>373</v>
+      </c>
+      <c r="E31" t="s">
+        <v>374</v>
+      </c>
+      <c r="F31" t="s">
+        <v>375</v>
+      </c>
+      <c r="G31" t="s">
+        <v>376</v>
+      </c>
+      <c r="H31" t="s">
+        <v>377</v>
+      </c>
+      <c r="I31" t="s">
+        <v>378</v>
+      </c>
+      <c r="J31" t="s">
+        <v>39</v>
+      </c>
+      <c r="K31" t="s">
+        <v>379</v>
+      </c>
+      <c r="L31" t="s">
+        <v>84</v>
+      </c>
+      <c r="M31" t="s">
+        <v>380</v>
+      </c>
+      <c r="N31" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>382</v>
+      </c>
+      <c r="B32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C32" t="s">
+        <v>384</v>
+      </c>
+      <c r="D32" t="s">
+        <v>385</v>
+      </c>
+      <c r="E32" t="s">
+        <v>386</v>
+      </c>
+      <c r="F32" t="s">
+        <v>387</v>
+      </c>
+      <c r="G32" t="s">
+        <v>388</v>
+      </c>
+      <c r="H32" t="s">
+        <v>389</v>
+      </c>
+      <c r="I32" t="s">
+        <v>390</v>
+      </c>
+      <c r="J32" t="s">
+        <v>39</v>
+      </c>
+      <c r="K32" t="s">
+        <v>391</v>
+      </c>
+      <c r="L32" t="s">
+        <v>96</v>
+      </c>
+      <c r="M32" t="s">
+        <v>392</v>
+      </c>
+      <c r="N32" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>394</v>
+      </c>
+      <c r="B33" t="s">
+        <v>395</v>
+      </c>
+      <c r="C33" t="s">
+        <v>396</v>
+      </c>
+      <c r="D33" t="s">
+        <v>397</v>
+      </c>
+      <c r="E33" t="s">
+        <v>398</v>
+      </c>
+      <c r="F33" t="s">
+        <v>399</v>
+      </c>
+      <c r="G33" t="s">
+        <v>400</v>
+      </c>
+      <c r="H33" t="s">
+        <v>401</v>
+      </c>
+      <c r="I33" t="s">
+        <v>402</v>
+      </c>
+      <c r="J33" t="s">
+        <v>39</v>
+      </c>
+      <c r="K33" t="s">
+        <v>403</v>
+      </c>
+      <c r="L33" t="s">
+        <v>109</v>
+      </c>
+      <c r="M33" t="s">
+        <v>404</v>
+      </c>
+      <c r="N33" t="s">
+        <v>29</v>
+      </c>
+      <c r="O33" t="s">
+        <v>405</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/NUMEX_pre_RStudio/models_leaf.xlsx
+++ b/NUMEX_pre_RStudio/models_leaf.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t xml:space="preserve">Modelo</t>
   </si>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">SLA | 1000 | Pouteria</t>
   </si>
   <si>
-    <t xml:space="preserve">79.56*** (SE = 2.95, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.60 (SE = 3.65, p = 0.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.58 (SE = 3.69, p = 0.88)</t>
+    <t xml:space="preserve">79.97*** (SE = 3.39, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00 (SE = 4.07, p = 1.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.72 (SE = 4.10, p = 0.86)</t>
   </si>
   <si>
     <t xml:space="preserve">0.00 (SE = , p = )</t>
   </si>
   <si>
-    <t xml:space="preserve">10.92 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
+    <t xml:space="preserve">11.47 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
   </si>
   <si>
     <t xml:space="preserve">0.001</t>
   </si>
   <si>
-    <t xml:space="preserve">269.4</t>
+    <t xml:space="preserve">241.4</t>
   </si>
   <si>
     <t xml:space="preserve">SLA | 1000 | Clarisia</t>
@@ -143,79 +143,79 @@
     <t xml:space="preserve">SLA | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">36.23*** (SE = 1.23, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.21 (SE = 1.26, p = 0.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.82 (SE = 1.24, p = 0.51)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.8</t>
+    <t xml:space="preserve">36.22*** (SE = 1.21, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.23 (SE = 1.22, p = 0.85)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.82 (SE = 1.20, p = 0.50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.3</t>
   </si>
   <si>
     <t xml:space="preserve">SLA | 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">35.77*** (SE = 0.77, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.37 (SE = 0.96, p = 0.70)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.80 (SE = 0.95, p = 0.40)</t>
+    <t xml:space="preserve">35.71*** (SE = 0.77, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.51 (SE = 0.97, p = 0.60)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.68 (SE = 0.96, p = 0.48)</t>
   </si>
   <si>
     <t xml:space="preserve">3.35 (SE = , p = )</t>
   </si>
   <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.9</t>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260.6</t>
   </si>
   <si>
     <t xml:space="preserve">SLA | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">69.34*** (SE = 4.36, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.85 (SE = 5.08, p = 0.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24 (SE = 5.04, p = 0.23)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.17 (SE = , p = )</t>
+    <t xml:space="preserve">69.89*** (SE = 4.35, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.76 (SE = 5.02, p = 0.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52 (SE = 5.06, p = 0.22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.13 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">21</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.2</t>
+    <t xml:space="preserve">0.237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.1</t>
   </si>
   <si>
     <t xml:space="preserve">SLA | 3000 | Weinmannia</t>
@@ -245,427 +245,430 @@
     <t xml:space="preserve">Thickness | 1000 | Pouteria</t>
   </si>
   <si>
+    <t xml:space="preserve">0.20*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00 (SE = 0.01, p = 0.63)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00 (SE = 0.01, p = 0.88)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.02 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-115.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thickness | 1000 | Clarisia</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.21*** (SE = 0.01, p = &lt;0.01)</t>
   </si>
   <si>
+    <t xml:space="preserve">-0.00 (SE = 0.00, p = 0.56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01+ (SE = 0.00, p = 0.06)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-40.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thickness | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.54*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00 (SE = 0.01, p = 0.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-107.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thickness | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
     <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.42)</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.00 (SE = 0.01, p = 0.60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-136.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thickness | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.00, p = 0.56)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01+ (SE = 0.00, p = 0.06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-40.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thickness | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.54*** (SE = 0.01, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01 (SE = 0.02, p = 0.57)</t>
+    <t xml:space="preserve">-0.00 (SE = 0.01, p = 0.84)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-185.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thickness | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.46*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = 0.02, p = 0.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = 0.02, p = 1.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.04 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-50.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thickness | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.26*** (SE = 0.01, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.02 (SE = 0.02, p = 0.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.00 (SE = 0.02, p = 0.97)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-44.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80*** (SE = 0.04, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05 (SE = 0.05, p = 0.31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00 (SE = 0.05, p = 0.98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.03 (SE = 0.08, p = 0.73)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05 (SE = 0.08, p = 0.57)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73*** (SE = 0.04, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.05 (SE = 0.04, p = 0.29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.07+ (SE = 0.04, p = 0.10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-22.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48*** (SE = 0.04, p = &lt;0.01)</t>
   </si>
   <si>
     <t xml:space="preserve">-0.00 (SE = 0.02, p = 0.91)</t>
   </si>
   <si>
-    <t xml:space="preserve">0.05 (SE = , p = )</t>
+    <t xml:space="preserve">-0.00 (SE = 0.03, p = 0.87)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.07 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-70.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.79*** (SE = 0.07, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10 (SE = 0.07, p = 0.17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.08 (SE = 0.07, p = 0.28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toughness | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.81*** (SE = 0.03, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 (SE = 0.04, p = 0.90)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.05 (SE = 0.04, p = 0.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-16.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.99*** (SE = 5.67, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.07 (SE = 6.83, p = 0.66)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.72 (SE = 6.87, p = 0.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.23 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 1000 | Clarisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.50*** (SE = 3.79, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.13 (SE = 3.84, p = 0.97)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.24 (SE = 3.93, p = 0.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 2000 | Alchornea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.66*** (SE = 2.17, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.87* (SE = 2.65, p = 0.03)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24 (SE = 2.63, p = 0.64)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA| 2000 | Myrcia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.60*** (SE = 1.17, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.39 (SE = 1.43, p = 0.79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.14 (SE = 1.43, p = 0.14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 3000 | Hedyosmum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.19*** (SE = 1.92, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.76+ (SE = 2.01, p = 0.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85 (SE = 2.03, p = 0.38)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA | 3000 | Weinmannia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50*** (SE = 0.15, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24 (SE = 0.17, p = 0.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.24 (SE = 0.17, p = 0.19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.35 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMC | 1000 | Pouteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">505.59*** (SE = 10.91, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41 (SE = 12.96, p = 0.68)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.72 (SE = 12.97, p = 0.84)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.28 (SE = , p = )</t>
   </si>
   <si>
     <t xml:space="preserve">0.007</t>
   </si>
   <si>
-    <t xml:space="preserve">-112.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thickness | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47*** (SE = 0.01, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01 (SE = 0.01, p = 0.50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.01, p = 0.95)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.03 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-189.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thickness | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46*** (SE = 0.01, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00 (SE = 0.02, p = 0.82)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.02, p = 0.87)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.04 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-50.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thickness | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26*** (SE = 0.01, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.02 (SE = 0.02, p = 0.32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.02, p = 0.97)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-44.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.79*** (SE = 0.04, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06 (SE = 0.04, p = 0.22)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.02 (SE = 0.04, p = 0.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-21.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.03 (SE = 0.08, p = 0.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05 (SE = 0.08, p = 0.57)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73*** (SE = 0.04, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.04 (SE = 0.04, p = 0.36)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.08+ (SE = 0.04, p = 0.06)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-25.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48*** (SE = 0.04, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.02, p = 0.96)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.00 (SE = 0.02, p = 0.92)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-73.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.80*** (SE = 0.07, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12 (SE = 0.07, p = 0.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.09 (SE = 0.07, p = 0.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toughness | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81*** (SE = 0.03, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.01 (SE = 0.04, p = 0.90)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.05 (SE = 0.04, p = 0.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-16.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.17*** (SE = 6.45, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3.51 (SE = 6.63, p = 0.60)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.89 (SE = 6.42, p = 0.77)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.62 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 1000 | Clarisia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.50*** (SE = 3.79, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.13 (SE = 3.84, p = 0.97)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.24 (SE = 3.93, p = 0.32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 2000 | Alchornea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.85*** (SE = 2.13, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.29* (SE = 2.56, p = 0.02)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77 (SE = 2.51, p = 0.49)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA| 2000 | Myrcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.56*** (SE = 1.17, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47 (SE = 1.41, p = 0.74)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.08 (SE = 1.41, p = 0.15)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.61 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 3000 | Hedyosmum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.90*** (SE = 1.82, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.40* (SE = 1.89, p = 0.03)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40 (SE = 1.89, p = 0.22)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA | 3000 | Weinmannia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50*** (SE = 0.15, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24 (SE = 0.17, p = 0.20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24 (SE = 0.17, p = 0.19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMC | 1000 | Pouteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">512.44*** (SE = 11.12, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11 (SE = 12.18, p = 0.62)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-13.52 (SE = 11.91, p = 0.26)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.78 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.69 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.3</t>
+    <t xml:space="preserve">0.019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.4</t>
   </si>
   <si>
     <t xml:space="preserve">DMC | 1000 | Clarisia</t>
@@ -692,67 +695,76 @@
     <t xml:space="preserve">DMC | 2000 | Alchornea</t>
   </si>
   <si>
-    <t xml:space="preserve">430.18*** (SE = 9.64, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.72 (SE = 7.72, p = 0.17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.28 (SE = 7.58, p = 0.97)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.42 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.10 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.0</t>
+    <t xml:space="preserve">430.14*** (SE = 9.76, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.66 (SE = 8.17, p = 0.20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.38 (SE = 8.07, p = 0.96)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.27 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.96 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">387.3</t>
   </si>
   <si>
     <t xml:space="preserve">DMC 2000 | Myrcia</t>
   </si>
   <si>
-    <t xml:space="preserve">488.35*** (SE = 5.88, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20 (SE = 7.30, p = 0.98)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-6.35 (SE = 7.27, p = 0.39)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.53 (SE = , p = )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">456.9</t>
+    <t xml:space="preserve">488.78*** (SE = 5.89, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.88 (SE = 7.36, p = 0.91)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.33 (SE = 7.33, p = 0.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.51 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447.4</t>
   </si>
   <si>
     <t xml:space="preserve">DMC | 3000 | Hedyosmum</t>
   </si>
   <si>
-    <t xml:space="preserve">279.41*** (SE = 9.97, p = &lt;0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.82+ (SE = 11.62, p = 0.08)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-33.08* (SE = 11.52, p = 0.01)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.0</t>
+    <t xml:space="preserve">277.20*** (SE = 10.60, p = &lt;0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.92 (SE = 11.75, p = 0.11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-32.37* (SE = 11.87, p = 0.01)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.01 (SE = , p = )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.3</t>
   </si>
   <si>
     <t xml:space="preserve">DMC | 3000 | Weinmannia</t>
@@ -1446,89 +1458,89 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E11" t="s">
         <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11" t="s">
         <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G12" t="s">
         <v>48</v>
       </c>
       <c r="H12" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I12" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="J12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" t="s">
         <v>57</v>
       </c>
       <c r="H13" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
         <v>22</v>
@@ -1586,7 +1598,7 @@
         <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G15" t="s">
         <v>73</v>
@@ -1650,39 +1662,39 @@
         <v>27</v>
       </c>
       <c r="F17" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G17" t="s">
         <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F18" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="G18" t="s">
         <v>48</v>
@@ -1714,13 +1726,13 @@
         <v>142</v>
       </c>
       <c r="F19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
       </c>
       <c r="H19" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="I19" t="s">
         <v>144</v>
@@ -1778,7 +1790,7 @@
         <v>27</v>
       </c>
       <c r="F21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G21" t="s">
         <v>73</v>
@@ -1807,112 +1819,112 @@
         <v>164</v>
       </c>
       <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" t="s">
         <v>165</v>
-      </c>
-      <c r="F22" t="s">
-        <v>166</v>
       </c>
       <c r="G22" t="s">
         <v>29</v>
       </c>
       <c r="H22" t="s">
-        <v>102</v>
+        <v>166</v>
       </c>
       <c r="I22" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" t="s">
         <v>167</v>
-      </c>
-      <c r="J22" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" t="s">
         <v>169</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>170</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>171</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>172</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>173</v>
-      </c>
-      <c r="F23" t="s">
-        <v>174</v>
       </c>
       <c r="G23" t="s">
         <v>38</v>
       </c>
       <c r="H23" t="s">
+        <v>174</v>
+      </c>
+      <c r="I23" t="s">
         <v>175</v>
       </c>
-      <c r="I23" t="s">
+      <c r="J23" t="s">
         <v>176</v>
-      </c>
-      <c r="J23" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" t="s">
         <v>178</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>179</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>180</v>
-      </c>
-      <c r="D24" t="s">
-        <v>181</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G24" t="s">
         <v>48</v>
       </c>
       <c r="H24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I24" t="s">
         <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B25" t="s">
         <v>185</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>186</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>187</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>188</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>189</v>
-      </c>
-      <c r="F25" t="s">
-        <v>190</v>
       </c>
       <c r="G25" t="s">
         <v>57</v>
       </c>
       <c r="H25" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="I25" t="s">
         <v>191</v>
@@ -1967,7 +1979,7 @@
         <v>205</v>
       </c>
       <c r="E27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F27" t="s">
         <v>206</v>
@@ -1976,205 +1988,205 @@
         <v>73</v>
       </c>
       <c r="H27" t="s">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="I27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C28" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D28" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E28" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F28" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G28" t="s">
         <v>29</v>
       </c>
       <c r="H28" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I28" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J28" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C29" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D29" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
       </c>
       <c r="F29" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G29" t="s">
         <v>38</v>
       </c>
       <c r="H29" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I29" t="s">
         <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C30" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D30" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E30" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F30" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G30" t="s">
         <v>48</v>
       </c>
       <c r="H30" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I30" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J30" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B31" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D31" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
       </c>
       <c r="F31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G31" t="s">
         <v>57</v>
       </c>
       <c r="H31" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I31" t="s">
         <v>22</v>
       </c>
       <c r="J31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C32" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D32" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>246</v>
       </c>
       <c r="F32" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G32" t="s">
         <v>65</v>
       </c>
       <c r="H32" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I32" t="s">
-        <v>22</v>
+        <v>249</v>
       </c>
       <c r="J32" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C33" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D33" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
       </c>
       <c r="F33" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G33" t="s">
         <v>73</v>
       </c>
       <c r="H33" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I33" t="s">
         <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
